--- a/samples/student_fake_sample.xlsx
+++ b/samples/student_fake_sample.xlsx
@@ -30,262 +30,262 @@
     <t>المرحلة</t>
   </si>
   <si>
+    <t xml:space="preserve">أسماء عاصم رامي عدي</t>
+  </si>
+  <si>
+    <t>بكلوريوس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أنس شريف مصطفى عزمي</t>
+  </si>
+  <si>
+    <t>ماجستير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">باسل نديم كريم هشام</t>
+  </si>
+  <si>
+    <t>دكتوراه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تالة غسان عماد رامي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحقيق حقي لؤي عنان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جومانا هشام رفعت عصام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دانا مالك رامز بهاء</t>
+  </si>
+  <si>
+    <t xml:space="preserve">راشد سيف مكتوم حمدان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رانيا فكري طلال سالم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">روعة سامي خيري عبدالغني</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ريناد فراس حاتم ساري</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زهراء جلال سعادة منصور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلمى جعفر أمين يوسف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سميح عطية لطفي جابر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سمير عدنان ياسين مؤيد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شكري عبدالوهاب جلاء فتحي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صلاح مأمون عارف حازم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عاصم حازم وليد صادق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عامر فكري زكي طاهر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبدالحميد ياسين رشدي عزمي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غادة أيمن جلال ثائر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غازي عودة مطر راكان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لؤي رياض صبحي جلال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لارا وسام سميح بسام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ليلى هاشم منير عبدالقادر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منير ثابت مجيد صبحي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ميسون مروان نصري حيدر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نائل سالم فوزي ماجد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ناصر جاسم عبدالكريم عودة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نبيل فواز عروة خالد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نور هادي عباس عيسى</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هبة سمير نبيل رافت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هند وائل عادل حاتم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وسيم لبيب سعيد طه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">أمل صبحي نديم بسام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">إبراهيم عيسى جعفر حسين</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جاسم حسن محمد راشد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حسن علي محمود أحمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دانا غانم سالم رشيد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ريم سالم حمادي نعيم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سعيد حميد سلطان عواد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلمى حسني شاكر عاطف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلمى مراد حاتم فواز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">طارق فؤاد حسين علي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبدالعزيز حمدان نايف عايد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عبدالله عمر خليفة سلطان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فهد ناصر تركي متعب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لينا زياد باسم طارق</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نور الدين بشير توفيق كمال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هند نادر مجدي حازم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ياسر نبيل عادل سمير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خالد سعيد عبدالله محمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خديجة خالد سيف راشد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زينب حمادة طه إسماعيل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سارة فهد عبدالعزيز أحمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عائشة صلاح الدين مازن ياسر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">علي حسن يوسف عبدالله</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عمر سليمان جاسم محمد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فاطمة محمود خالد عمر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محمد عبدالرحمن خالد سعيد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">محمود إبراهيم عمر سليمان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مريم عامر فهد ناصر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هدى جابر فراج علي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">يوسف عبدالله سعيد إبراهيم</t>
+  </si>
+  <si>
     <t xml:space="preserve">أحمد محمد علي حسن</t>
   </si>
   <si>
-    <t>بكلوريوس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أسماء عاصم رامي عدي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أمل صبحي نديم بسام</t>
-  </si>
-  <si>
-    <t xml:space="preserve">أنس شريف مصطفى عزمي</t>
-  </si>
-  <si>
-    <t>ماجستير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">إبراهيم عيسى جعفر حسين</t>
-  </si>
-  <si>
     <t xml:space="preserve">إبراهيم هشام عدنان قاسم</t>
   </si>
   <si>
-    <t xml:space="preserve">باسل نديم كريم هشام</t>
-  </si>
-  <si>
-    <t>دكتوراه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تالة غسان عماد رامي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تحقيق حقي لؤي عنان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جاسم حسن محمد راشد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جومانا هشام رفعت عصام</t>
-  </si>
-  <si>
     <t xml:space="preserve">حسن رياض غسان طلال</t>
   </si>
   <si>
-    <t xml:space="preserve">حسن علي محمود أحمد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خالد سعيد عبدالله محمد</t>
-  </si>
-  <si>
     <t xml:space="preserve">خالد وليد سمير نبيل</t>
   </si>
   <si>
-    <t xml:space="preserve">خديجة خالد سيف راشد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دانا غانم سالم رشيد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دانا مالك رامز بهاء</t>
-  </si>
-  <si>
     <t xml:space="preserve">دينا أيمن زهير منذر</t>
   </si>
   <si>
-    <t xml:space="preserve">راشد سيف مكتوم حمدان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رانيا فكري طلال سالم</t>
-  </si>
-  <si>
     <t xml:space="preserve">رنا فهد صلاح جابر</t>
   </si>
   <si>
-    <t xml:space="preserve">روعة سامي خيري عبدالغني</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ريم سالم حمادي نعيم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ريناد فراس حاتم ساري</t>
-  </si>
-  <si>
-    <t xml:space="preserve">زهراء جلال سعادة منصور</t>
-  </si>
-  <si>
     <t xml:space="preserve">زينب حسن حسين فاروق</t>
   </si>
   <si>
-    <t xml:space="preserve">زينب حمادة طه إسماعيل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سارة فهد عبدالعزيز أحمد</t>
-  </si>
-  <si>
     <t xml:space="preserve">سارة ماجد مروان لطفي</t>
   </si>
   <si>
     <t xml:space="preserve">سعد ناصر توفيق حمزة</t>
   </si>
   <si>
-    <t xml:space="preserve">سعيد حميد سلطان عواد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سلمى جعفر أمين يوسف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سلمى حسني شاكر عاطف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سلمى مراد حاتم فواز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سميح عطية لطفي جابر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سمير عدنان ياسين مؤيد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شكري عبدالوهاب جلاء فتحي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صلاح مأمون عارف حازم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">طارق فؤاد حسين علي</t>
-  </si>
-  <si>
     <t xml:space="preserve">عائشة سلطان عماد ياسر</t>
   </si>
   <si>
-    <t xml:space="preserve">عائشة صلاح الدين مازن ياسر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عاصم حازم وليد صادق</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عامر فكري زكي طاهر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عبدالحميد ياسين رشدي عزمي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عبدالعزيز حمدان نايف عايد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عبدالله عمر خليفة سلطان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">علي حسن يوسف عبدالله</t>
-  </si>
-  <si>
     <t xml:space="preserve">علي رضا سامي عصام</t>
   </si>
   <si>
-    <t xml:space="preserve">عمر سليمان جاسم محمد</t>
-  </si>
-  <si>
     <t xml:space="preserve">عمر عبد الله سعيد محمود</t>
   </si>
   <si>
-    <t xml:space="preserve">غادة أيمن جلال ثائر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غازي عودة مطر راكان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فاطمة محمود خالد عمر</t>
-  </si>
-  <si>
     <t xml:space="preserve">فاطمة يوسف إبراهيم خالد</t>
   </si>
   <si>
-    <t xml:space="preserve">فهد ناصر تركي متعب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لؤي رياض صبحي جلال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لارا وسام سميح بسام</t>
-  </si>
-  <si>
     <t xml:space="preserve">ليلى بسام منير وديع</t>
   </si>
   <si>
-    <t xml:space="preserve">ليلى هاشم منير عبدالقادر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لينا زياد باسم طارق</t>
-  </si>
-  <si>
     <t xml:space="preserve">محمد إياس نادر شريف</t>
   </si>
   <si>
-    <t xml:space="preserve">محمد عبدالرحمن خالد سعيد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">محمود إبراهيم عمر سليمان</t>
-  </si>
-  <si>
     <t xml:space="preserve">محمود سليم رائد باسل</t>
   </si>
   <si>
     <t xml:space="preserve">مريم طارق زياد أنور</t>
   </si>
   <si>
-    <t xml:space="preserve">مريم عامر فهد ناصر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منير ثابت مجيد صبحي</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ميسون مروان نصري حيدر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نائل سالم فوزي ماجد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ناصر جاسم عبدالكريم عودة</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نبيل فواز عروة خالد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نور الدين بشير توفيق كمال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نور هادي عباس عيسى</t>
-  </si>
-  <si>
     <t xml:space="preserve">نور هاشم جمال فيصل</t>
   </si>
   <si>
-    <t xml:space="preserve">هبة سمير نبيل رافت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هدى جابر فراج علي</t>
-  </si>
-  <si>
     <t xml:space="preserve">هدى كريم مجدي أسعد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هند نادر مجدي حازم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هند وائل عادل حاتم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وسيم لبيب سعيد طه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ياسر نبيل عادل سمير</t>
-  </si>
-  <si>
-    <t xml:space="preserve">يوسف عبدالله سعيد إبراهيم</t>
   </si>
   <si>
     <t xml:space="preserve">يوسف مصطفى كمال رشيد</t>
@@ -886,24 +886,24 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C2" s="3" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>2024</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -911,26 +911,26 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
+        <v>2022</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
+      <c r="A5" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C5" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1">
@@ -939,114 +939,114 @@
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C6" s="3" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
+        <v>2024</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D7" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>2024</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>2025</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1">
         <v>2025</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="1">
         <v>2024</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>9</v>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
+        <v>2024</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="14.25">
@@ -1054,290 +1054,290 @@
         <v>19</v>
       </c>
       <c r="B14" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>5</v>
+        <v>2022</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
+        <v>2024</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D15" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C16" s="3" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>5</v>
+        <v>2024</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D17" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="1">
         <v>2024</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="1">
         <v>2024</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25">
-      <c r="A20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="1">
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="1">
         <v>2025</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25">
-      <c r="A24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1">
+      <c r="C30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="1">
         <v>2025</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25">
-      <c r="A25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25">
-      <c r="A28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="A29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25">
-      <c r="A30" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25">
-      <c r="A31" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B34" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>13</v>
+        <v>2024</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -1350,21 +1350,21 @@
       <c r="B35" s="1">
         <v>2024</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>5</v>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B36" s="1">
         <v>2024</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="1">
@@ -1372,45 +1372,45 @@
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B37" s="1">
         <v>2024</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>9</v>
+      <c r="C37" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B38" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C38" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B39" s="1">
         <v>2024</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>9</v>
+      <c r="C39" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" ht="14.25">
@@ -1420,21 +1420,21 @@
       <c r="B40" s="1">
         <v>2024</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>9</v>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B41" s="1">
         <v>2024</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="1">
@@ -1442,17 +1442,17 @@
       </c>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B42" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C42" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D42" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" ht="14.25">
@@ -1460,27 +1460,27 @@
         <v>48</v>
       </c>
       <c r="B43" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C43" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D43" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B44" s="1">
         <v>2024</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>9</v>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" ht="14.25">
@@ -1490,35 +1490,35 @@
       <c r="B45" s="1">
         <v>2024</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>9</v>
+      <c r="C45" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B46" s="1">
         <v>2024</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>9</v>
+      <c r="C46" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B47" s="1">
         <v>2024</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D47" s="1">
@@ -1526,13 +1526,13 @@
       </c>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B48" s="1">
         <v>2024</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D48" s="1">
@@ -1540,97 +1540,97 @@
       </c>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B49" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="1">
         <v>2023</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="1">
+      <c r="C53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="50" ht="14.25">
-      <c r="A50" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25">
-      <c r="A51" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="1">
+    <row r="54" ht="14.25">
+      <c r="A54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="1">
         <v>2023</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="1">
+      <c r="C54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="52" ht="14.25">
-      <c r="A52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" ht="14.25">
-      <c r="A53" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" ht="14.25">
-      <c r="A54" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1</v>
-      </c>
-    </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B55" s="1">
         <v>2023</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D55" s="1">
@@ -1638,125 +1638,125 @@
       </c>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B56" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C56" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D56" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B57" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C57" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D57" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B58" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>9</v>
+        <v>2023</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="1" t="s">
         <v>64</v>
       </c>
       <c r="B59" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>9</v>
+        <v>2023</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B60" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C60" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D60" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B61" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>9</v>
+        <v>2023</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B62" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C62" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D62" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B63" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C63" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D63" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B64" s="1">
         <v>2023</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="1">
@@ -1770,7 +1770,7 @@
       <c r="B65" s="1">
         <v>2023</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D65" s="1">
@@ -1778,13 +1778,13 @@
       </c>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B66" s="1">
         <v>2022</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D66" s="1">
@@ -1792,13 +1792,13 @@
       </c>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B67" s="1">
         <v>2022</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D67" s="1">
@@ -1806,125 +1806,125 @@
       </c>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B68" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C68" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D68" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B69" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>13</v>
+        <v>2022</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D69" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B70" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D70" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B71" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D71" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B72" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C72" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D72" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B73" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D73" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B74" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C74" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D74" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B75" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D75" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B76" s="1">
         <v>2022</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D76" s="1">
@@ -1936,13 +1936,13 @@
         <v>82</v>
       </c>
       <c r="B77" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C77" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D77" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" ht="14.25">
@@ -1950,23 +1950,23 @@
         <v>83</v>
       </c>
       <c r="B78" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C78" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D78" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B79" s="1">
         <v>2022</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D79" s="1">
@@ -1974,73 +1974,73 @@
       </c>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B80" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C80" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D80" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B81" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>9</v>
+        <v>2022</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D81" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B82" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>13</v>
+        <v>2022</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="D82" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B83" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C83" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D83" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B84" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C84" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D84" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" ht="14.25">
@@ -2050,7 +2050,7 @@
       <c r="B85" s="1">
         <v>2022</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D85" s="1">
@@ -2065,7 +2065,7 @@
     </row>
   </sheetData>
   <sortState ref="A2:D85" columnSort="0">
-    <sortCondition sortBy="value" descending="0" ref="A1:A84"/>
+    <sortCondition sortBy="value" descending="0" ref="D2:D85"/>
   </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/samples/student_fake_sample.xlsx
+++ b/samples/student_fake_sample.xlsx
@@ -349,16 +349,13 @@
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -882,7 +879,7 @@
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1">
@@ -1368,6 +1365,9 @@
         <v>5</v>
       </c>
       <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36">
         <v>2</v>
       </c>
     </row>
@@ -1382,6 +1382,9 @@
         <v>5</v>
       </c>
       <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37">
         <v>2</v>
       </c>
     </row>
@@ -1396,6 +1399,9 @@
         <v>5</v>
       </c>
       <c r="D38" s="1">
+        <v>3</v>
+      </c>
+      <c r="E38">
         <v>2</v>
       </c>
     </row>
@@ -1410,6 +1416,9 @@
         <v>5</v>
       </c>
       <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39">
         <v>2</v>
       </c>
     </row>
@@ -1424,6 +1433,9 @@
         <v>5</v>
       </c>
       <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40">
         <v>2</v>
       </c>
     </row>

--- a/samples/student_fake_sample.xlsx
+++ b/samples/student_fake_sample.xlsx
@@ -16,12 +16,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>الطالب</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سنة التسجيل</t>
   </si>
   <si>
     <t xml:space="preserve">الدرجة العلمية</t>
@@ -859,9 +856,8 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="1" width="33.140625"/>
-    <col customWidth="1" min="2" max="2" style="1" width="19.7109375"/>
-    <col customWidth="1" min="3" max="3" style="1" width="25.7109375"/>
-    <col customWidth="1" min="4" max="4" style="1" width="24.8515625"/>
+    <col customWidth="1" min="2" max="2" style="1" width="25.7109375"/>
+    <col customWidth="1" min="3" max="3" style="1" width="24.8515625"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="36.75" customHeight="1">
@@ -874,1198 +870,928 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="1">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="1">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="1">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1">
+        <v>21</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="1">
+        <v>22</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="1">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="1">
+        <v>24</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="21" ht="14.25">
       <c r="A21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1">
+        <v>25</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="1">
+        <v>26</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="1">
+        <v>27</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="1">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="1">
+        <v>29</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="14.25">
       <c r="A26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="1">
+        <v>30</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="14.25">
       <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="1">
+        <v>31</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="14.25">
       <c r="A28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="1">
+        <v>32</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="14.25">
       <c r="A29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="1">
+        <v>33</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="1">
+        <v>34</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="14.25">
       <c r="A31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="1">
+        <v>35</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="14.25">
       <c r="A32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="1">
+        <v>36</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="1">
+        <v>37</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="14.25">
       <c r="A34" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="1">
+        <v>38</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="14.25">
       <c r="A35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="1">
+        <v>39</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="1">
+        <v>40</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="1">
         <v>3</v>
-      </c>
-      <c r="E36">
-        <v>2</v>
       </c>
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="1">
+        <v>41</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="1">
         <v>3</v>
-      </c>
-      <c r="E37">
-        <v>2</v>
       </c>
     </row>
     <row r="38" ht="14.25">
       <c r="A38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="1">
+        <v>42</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="1">
         <v>3</v>
-      </c>
-      <c r="E38">
-        <v>2</v>
       </c>
     </row>
     <row r="39" ht="14.25">
       <c r="A39" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="1">
+        <v>43</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="1">
         <v>3</v>
-      </c>
-      <c r="E39">
-        <v>2</v>
       </c>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="1">
+        <v>44</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="1">
         <v>3</v>
-      </c>
-      <c r="E40">
-        <v>2</v>
       </c>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="1">
+        <v>45</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="1">
+        <v>46</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="1">
+        <v>47</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="44" ht="14.25">
       <c r="A44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="1">
+        <v>48</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="45" ht="14.25">
       <c r="A45" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="1">
+        <v>49</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="46" ht="14.25">
       <c r="A46" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="1">
+        <v>50</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="1">
+        <v>51</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="1">
+        <v>52</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="1">
+        <v>53</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="50" ht="14.25">
       <c r="A50" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="1">
+        <v>54</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="51" ht="14.25">
       <c r="A51" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="1">
+        <v>55</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="52" ht="14.25">
       <c r="A52" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="1">
+        <v>56</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="53" ht="14.25">
       <c r="A53" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="1">
+        <v>57</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="54" ht="14.25">
       <c r="A54" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="1">
+        <v>58</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="55" ht="14.25">
       <c r="A55" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B55" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="1">
+        <v>59</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="56" ht="14.25">
       <c r="A56" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="1">
+        <v>60</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="57" ht="14.25">
       <c r="A57" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B57" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="1">
+        <v>61</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="58" ht="14.25">
       <c r="A58" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="1">
+        <v>62</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="59" ht="14.25">
       <c r="A59" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B59" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="1">
+        <v>63</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="60" ht="14.25">
       <c r="A60" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="1">
+        <v>64</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="61" ht="14.25">
       <c r="A61" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="1">
+        <v>65</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="62" ht="14.25">
       <c r="A62" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="1">
+        <v>66</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="63" ht="14.25">
       <c r="A63" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="1">
+        <v>67</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="64" ht="14.25">
       <c r="A64" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" s="1">
+        <v>68</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="65" ht="14.25">
       <c r="A65" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B65" s="1">
-        <v>2023</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="1">
+        <v>69</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="66" ht="14.25">
       <c r="A66" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B66" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="1">
+        <v>70</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="67" ht="14.25">
       <c r="A67" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B67" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="1">
+        <v>71</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="68" ht="14.25">
       <c r="A68" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B68" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="1">
+        <v>72</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="69" ht="14.25">
       <c r="A69" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B69" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="1">
+        <v>73</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="70" ht="14.25">
       <c r="A70" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B70" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="1">
+        <v>74</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B71" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="1">
+        <v>75</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="72" ht="14.25">
       <c r="A72" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B72" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="1">
+        <v>76</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="73" ht="14.25">
       <c r="A73" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B73" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="1">
+        <v>77</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="74" ht="14.25">
       <c r="A74" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="1">
+        <v>78</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="75" ht="14.25">
       <c r="A75" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B75" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="1">
+        <v>79</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="76" ht="14.25">
       <c r="A76" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B76" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="1">
+        <v>80</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="77" ht="14.25">
       <c r="A77" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B77" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="1">
+        <v>81</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="78" ht="14.25">
       <c r="A78" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="1">
+        <v>82</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="79" ht="14.25">
       <c r="A79" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B79" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="1">
+        <v>83</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="80" ht="14.25">
       <c r="A80" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B80" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D80" s="1">
+        <v>84</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="81" ht="14.25">
       <c r="A81" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D81" s="1">
+        <v>85</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="82" ht="14.25">
       <c r="A82" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B82" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="1">
+        <v>86</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="83" ht="14.25">
       <c r="A83" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="1">
+        <v>87</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="84" ht="14.25">
       <c r="A84" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D84" s="1">
+        <v>88</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="85" ht="14.25">
       <c r="A85" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B85" s="1">
-        <v>2022</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" s="1">
+        <v>89</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" s="1">
         <v>4</v>
       </c>
     </row>
@@ -2073,11 +1799,10 @@
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:D85" columnSort="0">
-    <sortCondition sortBy="value" descending="0" ref="D2:D85"/>
+  <sortState ref="A2:C85" columnSort="0">
+    <sortCondition sortBy="value" descending="0" ref="C2:C85"/>
   </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
